--- a/artfynd/S 489-2024 artfynd.xlsx
+++ b/artfynd/S 489-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY49"/>
+  <dimension ref="A1:AZ49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5169790</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,6 +915,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126035415</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1016,6 +1031,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127298897</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1135,6 +1155,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126035425</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1246,6 +1271,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127830770</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1357,6 +1387,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127830773</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1454,6 +1489,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118991521</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1555,6 +1595,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135056018</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1661,6 +1706,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135056033</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1762,6 +1812,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135056048</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1863,6 +1918,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135056023</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1964,6 +2024,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135056021</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2065,6 +2130,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135056031</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2166,6 +2236,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135056037</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2267,6 +2342,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135056039</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2368,6 +2448,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135056042</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2469,6 +2554,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135056020</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2570,6 +2660,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135056022</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2671,6 +2766,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135056029</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2772,6 +2872,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135056035</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2873,6 +2978,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135056038</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2974,6 +3084,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135056043</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3075,6 +3190,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135056051</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3176,6 +3296,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135056026</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3277,6 +3402,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135056049</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3383,6 +3513,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118991522</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3484,6 +3619,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135056024</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3585,6 +3725,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135056025</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3686,6 +3831,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135056027</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3787,6 +3937,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135056028</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3888,6 +4043,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135056040</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3989,6 +4149,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135056046</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4090,6 +4255,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135056032</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4191,6 +4361,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135056034</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4292,6 +4467,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135056041</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4413,6 +4593,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127298705</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4524,6 +4709,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127830716</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4635,6 +4825,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127830713</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4751,6 +4946,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127830712</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4862,6 +5062,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127298861</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4982,6 +5187,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127298867</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5096,6 +5306,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104442000</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5210,6 +5425,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104441998</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5324,6 +5544,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104441999</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5438,6 +5663,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104442001</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5547,6 +5777,11 @@
       <c r="AY47" t="inlineStr">
         <is>
           <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127830755</t>
         </is>
       </c>
     </row>
@@ -5664,6 +5899,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126561347</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5780,8 +6020,63 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127298866</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 489-2024 artfynd.xlsx
+++ b/artfynd/S 489-2024 artfynd.xlsx
@@ -1500,7 +1500,7 @@
         <v>135056018</v>
       </c>
       <c r="B9" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>135056033</v>
       </c>
       <c r="B10" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>135056048</v>
       </c>
       <c r="B11" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>135056023</v>
       </c>
       <c r="B12" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>135056021</v>
       </c>
       <c r="B13" t="n">
-        <v>99219</v>
+        <v>99266</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>135056031</v>
       </c>
       <c r="B14" t="n">
-        <v>99533</v>
+        <v>99580</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>135056037</v>
       </c>
       <c r="B15" t="n">
-        <v>99533</v>
+        <v>99580</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>135056039</v>
       </c>
       <c r="B16" t="n">
-        <v>108274</v>
+        <v>108330</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>135056042</v>
       </c>
       <c r="B17" t="n">
-        <v>108274</v>
+        <v>108330</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>135056020</v>
       </c>
       <c r="B18" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>135056022</v>
       </c>
       <c r="B19" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>135056029</v>
       </c>
       <c r="B20" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>135056035</v>
       </c>
       <c r="B21" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>135056038</v>
       </c>
       <c r="B22" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>135056043</v>
       </c>
       <c r="B23" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>135056051</v>
       </c>
       <c r="B24" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>135056026</v>
       </c>
       <c r="B25" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>135056049</v>
       </c>
       <c r="B26" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>135056024</v>
       </c>
       <c r="B28" t="n">
-        <v>99472</v>
+        <v>99519</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>135056025</v>
       </c>
       <c r="B29" t="n">
-        <v>99472</v>
+        <v>99519</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         <v>135056027</v>
       </c>
       <c r="B30" t="n">
-        <v>99472</v>
+        <v>99519</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>135056028</v>
       </c>
       <c r="B31" t="n">
-        <v>99472</v>
+        <v>99519</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>135056040</v>
       </c>
       <c r="B32" t="n">
-        <v>99472</v>
+        <v>99519</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>135056046</v>
       </c>
       <c r="B33" t="n">
-        <v>99472</v>
+        <v>99519</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>135056032</v>
       </c>
       <c r="B34" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>135056034</v>
       </c>
       <c r="B35" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>135056041</v>
       </c>
       <c r="B36" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/S 489-2024 artfynd.xlsx
+++ b/artfynd/S 489-2024 artfynd.xlsx
@@ -1500,7 +1500,7 @@
         <v>135056018</v>
       </c>
       <c r="B9" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>135056033</v>
       </c>
       <c r="B10" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>135056048</v>
       </c>
       <c r="B11" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>135056023</v>
       </c>
       <c r="B12" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>135056021</v>
       </c>
       <c r="B13" t="n">
-        <v>99266</v>
+        <v>99293</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>135056031</v>
       </c>
       <c r="B14" t="n">
-        <v>99580</v>
+        <v>99607</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>135056037</v>
       </c>
       <c r="B15" t="n">
-        <v>99580</v>
+        <v>99607</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>135056039</v>
       </c>
       <c r="B16" t="n">
-        <v>108330</v>
+        <v>108357</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>135056042</v>
       </c>
       <c r="B17" t="n">
-        <v>108330</v>
+        <v>108357</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>135056020</v>
       </c>
       <c r="B18" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>135056022</v>
       </c>
       <c r="B19" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>135056029</v>
       </c>
       <c r="B20" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>135056035</v>
       </c>
       <c r="B21" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>135056038</v>
       </c>
       <c r="B22" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>135056043</v>
       </c>
       <c r="B23" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>135056051</v>
       </c>
       <c r="B24" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>135056026</v>
       </c>
       <c r="B25" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>135056049</v>
       </c>
       <c r="B26" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>135056024</v>
       </c>
       <c r="B28" t="n">
-        <v>99519</v>
+        <v>99546</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>135056025</v>
       </c>
       <c r="B29" t="n">
-        <v>99519</v>
+        <v>99546</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         <v>135056027</v>
       </c>
       <c r="B30" t="n">
-        <v>99519</v>
+        <v>99546</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>135056028</v>
       </c>
       <c r="B31" t="n">
-        <v>99519</v>
+        <v>99546</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>135056040</v>
       </c>
       <c r="B32" t="n">
-        <v>99519</v>
+        <v>99546</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>135056046</v>
       </c>
       <c r="B33" t="n">
-        <v>99519</v>
+        <v>99546</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>135056032</v>
       </c>
       <c r="B34" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>135056034</v>
       </c>
       <c r="B35" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>135056041</v>
       </c>
       <c r="B36" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
